--- a/sample-data/vessel-report.xlsx
+++ b/sample-data/vessel-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="63">
   <si>
     <t>MV AURORA — MONTHLY PREPAID CARD REPORT</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Card Product</t>
   </si>
   <si>
+    <t>Client</t>
+  </si>
+  <si>
     <t>Vessel / Office</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>Crew Name</t>
   </si>
   <si>
+    <t>Crew No.</t>
+  </si>
+  <si>
     <t>Date Issued</t>
   </si>
   <si>
@@ -52,10 +58,13 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>54105000001841</t>
-  </si>
-  <si>
-    <t>USD Reloadable Card</t>
+    <t>54109000001841</t>
+  </si>
+  <si>
+    <t>Monavate USD Reloadable</t>
+  </si>
+  <si>
+    <t>Oceanic Shipping Ltd</t>
   </si>
   <si>
     <t>MV Aurora</t>
@@ -67,64 +76,76 @@
     <t>A. Santos</t>
   </si>
   <si>
+    <t>CRW-04821</t>
+  </si>
+  <si>
     <t>15/06/2026</t>
   </si>
   <si>
     <t>31/12/2028</t>
   </si>
   <si>
-    <t>B-54105</t>
+    <t>B-54109</t>
   </si>
   <si>
     <t>Handed over at crew change</t>
   </si>
   <si>
-    <t>54105000001842</t>
+    <t>54109000001842</t>
   </si>
   <si>
     <t>R. Dela Cruz</t>
   </si>
   <si>
-    <t>54105000001843</t>
+    <t>CRW-04822</t>
+  </si>
+  <si>
+    <t>54109000001843</t>
   </si>
   <si>
     <t>M. Reyes</t>
   </si>
   <si>
-    <t>54105000001844</t>
+    <t>CRW-04823</t>
+  </si>
+  <si>
+    <t>54109000001844</t>
   </si>
   <si>
     <t>J. Bautista</t>
   </si>
   <si>
-    <t>54105000001845</t>
+    <t>CRW-04824</t>
+  </si>
+  <si>
+    <t>54109000001845</t>
   </si>
   <si>
     <t>L. García</t>
   </si>
   <si>
-    <t>54105000001846</t>
-  </si>
-  <si>
-    <t>P. Novak</t>
-  </si>
-  <si>
-    <t>54105000001847</t>
+    <t>CRW-04825</t>
+  </si>
+  <si>
+    <t>54109000001846</t>
+  </si>
+  <si>
+    <t>54109000001847</t>
   </si>
   <si>
     <t>available</t>
   </si>
   <si>
-    <t>54105000001848</t>
-  </si>
-  <si>
-    <t>54105000001849</t>
-  </si>
-  <si>
-    <t>54105000001850</t>
-  </si>
-  <si>
-    <t>54105000001851</t>
+    <t>54109000001848</t>
+  </si>
+  <si>
+    <t>54109000001849</t>
+  </si>
+  <si>
+    <t>54109000001850</t>
+  </si>
+  <si>
+    <t>54109000001851</t>
   </si>
   <si>
     <t>MISSING</t>
@@ -567,11 +588,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="9" width="22" customWidth="1"/>
+    <col min="2" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -590,7 +611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -618,602 +639,728 @@
       <c r="I4" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="H5" t="s">
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="I5" t="s">
+      <c r="G10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="H10" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="I10" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="J10" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="K10" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J16" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J17" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J18" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2</v>
-      </c>
       <c r="F20" t="s">
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J20" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
         <v>49</v>
       </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
         <v>50</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" t="s">
         <v>51</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J24" t="s">
+        <v>50</v>
+      </c>
+      <c r="K24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s">
         <v>2</v>
@@ -1225,7 +1372,13 @@
         <v>2</v>
       </c>
       <c r="I25" t="s">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
